--- a/data/pack/us/diesel.xlsx
+++ b/data/pack/us/diesel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1700"/>
+  <dimension ref="A1:K1701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -93934,6 +93934,61 @@
         </is>
       </c>
       <c r="K1700" t="inlineStr">
+        <is>
+          <t>Source: U.S. Energy Information Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>Gasóleo de automoción (surtidor)</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E1701" t="n">
+        <v>6.179</v>
+      </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>gal</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H1701" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1701" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration (Open Data API)</t>
+        </is>
+      </c>
+      <c r="J1701" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K1701" t="inlineStr">
         <is>
           <t>Source: U.S. Energy Information Administration</t>
         </is>
@@ -94033,7 +94088,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -94044,7 +94099,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="9">
@@ -94139,7 +94194,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/diesel.xlsx
+++ b/data/pack/us/diesel.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1701"/>
+  <dimension ref="A1:K1702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -93989,6 +93989,61 @@
         </is>
       </c>
       <c r="K1701" t="inlineStr">
+        <is>
+          <t>Source: U.S. Energy Information Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>Gasóleo de automoción (surtidor)</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E1702" t="n">
+        <v>6.276</v>
+      </c>
+      <c r="F1702" t="inlineStr">
+        <is>
+          <t>gal</t>
+        </is>
+      </c>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H1702" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1702" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration (Open Data API)</t>
+        </is>
+      </c>
+      <c r="J1702" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K1702" t="inlineStr">
         <is>
           <t>Source: U.S. Energy Information Administration</t>
         </is>
@@ -94088,7 +94143,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -94099,7 +94154,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="9">
@@ -94194,7 +94249,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/data/pack/us/diesel.xlsx
+++ b/data/pack/us/diesel.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1702"/>
+  <dimension ref="A1:K1703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -94044,6 +94044,61 @@
         </is>
       </c>
       <c r="K1702" t="inlineStr">
+        <is>
+          <t>Source: U.S. Energy Information Administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>Gasóleo de automoción (surtidor)</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1703" t="n">
+        <v>6.352</v>
+      </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>gal</t>
+        </is>
+      </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H1703" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1703" t="inlineStr">
+        <is>
+          <t>U.S. Energy Information Administration (Open Data API)</t>
+        </is>
+      </c>
+      <c r="J1703" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K1703" t="inlineStr">
         <is>
           <t>Source: U.S. Energy Information Administration</t>
         </is>
@@ -94143,7 +94198,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -94154,7 +94209,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="9">
@@ -94249,7 +94304,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
